--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Atlantic-Foods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588241FD-48CC-4441-A8E8-5AB915F170FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A49531D-A542-44BB-941E-59B5A9CB3FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -11142,10 +11142,10 @@
         <v>31</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H377">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H377" s="2">
+        <v>1.0011574074074074E-2</v>
       </c>
       <c r="I377" s="1">
         <v>46176.469907407409</v>
@@ -11183,7 +11183,7 @@
         <v>46176.470601851855</v>
       </c>
       <c r="J378">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K378" t="s">
         <v>11</v>
@@ -11215,7 +11215,7 @@
         <v>46176.470601851855</v>
       </c>
       <c r="J379">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K379" t="s">
         <v>11</v>
@@ -11244,7 +11244,7 @@
         <v>46176.470601851855</v>
       </c>
       <c r="J380">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K380" t="s">
         <v>11</v>
@@ -11316,7 +11316,7 @@
         <v>46176.471296296295</v>
       </c>
       <c r="J383">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K383" t="s">
         <v>11</v>
@@ -11345,7 +11345,7 @@
         <v>46176.471990740742</v>
       </c>
       <c r="J384">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K384" t="s">
         <v>11</v>
@@ -11377,7 +11377,7 @@
         <v>46176.471990740742</v>
       </c>
       <c r="J385">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K385" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Atlantic-Foods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3BB08B3-1FF4-4CAB-8E37-06988B80914C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49CCAAC8-96C3-4D9D-88E4-626C52B8DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="65">
   <si>
     <t>Company Name</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -1152,7 +1152,7 @@
       <c r="I22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" s="1">
@@ -11189,10 +11189,10 @@
         <v>29</v>
       </c>
       <c r="I378" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J378">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J378" s="2">
+        <v>1.1967592592592592E-2</v>
       </c>
       <c r="K378" s="1">
         <v>46176.470601851855</v>
@@ -11432,58 +11432,289 @@
       </c>
     </row>
     <row r="387" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H387" s="2"/>
-      <c r="I387" s="1"/>
-      <c r="J387" s="2"/>
-      <c r="K387" s="1"/>
+      <c r="D387" t="s">
+        <v>36</v>
+      </c>
+      <c r="E387">
+        <v>5104</v>
+      </c>
+      <c r="F387" t="s">
+        <v>61</v>
+      </c>
+      <c r="H387" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J387" s="2">
+        <v>0</v>
+      </c>
+      <c r="K387" s="1">
+        <v>46213.805555555555</v>
+      </c>
+      <c r="L387">
+        <v>0</v>
+      </c>
+      <c r="M387" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="388" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H388" s="2"/>
-      <c r="I388" s="1"/>
-      <c r="J388" s="2"/>
-      <c r="K388" s="1"/>
+      <c r="D388" t="s">
+        <v>36</v>
+      </c>
+      <c r="E388">
+        <v>1861</v>
+      </c>
+      <c r="F388" t="s">
+        <v>40</v>
+      </c>
+      <c r="G388" t="s">
+        <v>38</v>
+      </c>
+      <c r="H388" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J388" s="2">
+        <v>0</v>
+      </c>
+      <c r="K388" s="1">
+        <v>46213.806250000001</v>
+      </c>
+      <c r="L388">
+        <v>0</v>
+      </c>
+      <c r="M388" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="389" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H389" s="2"/>
-      <c r="I389" s="1"/>
-      <c r="J389" s="2"/>
-      <c r="K389" s="1"/>
+      <c r="D389" t="s">
+        <v>36</v>
+      </c>
+      <c r="E389">
+        <v>1868</v>
+      </c>
+      <c r="F389" t="s">
+        <v>41</v>
+      </c>
+      <c r="G389" t="s">
+        <v>38</v>
+      </c>
+      <c r="H389" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J389" s="2">
+        <v>0</v>
+      </c>
+      <c r="K389" s="1">
+        <v>46213.806944444441</v>
+      </c>
+      <c r="L389">
+        <v>0</v>
+      </c>
+      <c r="M389" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="390" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H390" s="2"/>
-      <c r="I390" s="1"/>
-      <c r="J390" s="2"/>
-      <c r="K390" s="1"/>
+      <c r="D390" t="s">
+        <v>36</v>
+      </c>
+      <c r="E390">
+        <v>1862</v>
+      </c>
+      <c r="F390" t="s">
+        <v>43</v>
+      </c>
+      <c r="G390" t="s">
+        <v>38</v>
+      </c>
+      <c r="H390" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J390" s="2">
+        <v>0</v>
+      </c>
+      <c r="K390" s="1">
+        <v>46213.806944444441</v>
+      </c>
+      <c r="L390">
+        <v>0</v>
+      </c>
+      <c r="M390" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="391" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H391" s="2"/>
-      <c r="I391" s="1"/>
-      <c r="J391" s="2"/>
-      <c r="K391" s="1"/>
+      <c r="D391" t="s">
+        <v>36</v>
+      </c>
+      <c r="E391">
+        <v>1863</v>
+      </c>
+      <c r="F391" t="s">
+        <v>45</v>
+      </c>
+      <c r="G391" t="s">
+        <v>38</v>
+      </c>
+      <c r="H391" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I391" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J391" s="2">
+        <v>0</v>
+      </c>
+      <c r="K391" s="1">
+        <v>46213.807638888888</v>
+      </c>
+      <c r="L391">
+        <v>0</v>
+      </c>
+      <c r="M391" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="392" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H392" s="2"/>
-      <c r="I392" s="1"/>
-      <c r="J392" s="2"/>
-      <c r="K392" s="1"/>
+      <c r="D392" t="s">
+        <v>36</v>
+      </c>
+      <c r="E392">
+        <v>1865</v>
+      </c>
+      <c r="F392" t="s">
+        <v>46</v>
+      </c>
+      <c r="G392" t="s">
+        <v>38</v>
+      </c>
+      <c r="H392" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I392" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J392" s="2">
+        <v>0</v>
+      </c>
+      <c r="K392" s="1">
+        <v>46213.808333333334</v>
+      </c>
+      <c r="L392">
+        <v>0</v>
+      </c>
+      <c r="M392" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="393" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H393" s="2"/>
-      <c r="I393" s="1"/>
-      <c r="J393" s="2"/>
-      <c r="K393" s="1"/>
+      <c r="D393" t="s">
+        <v>36</v>
+      </c>
+      <c r="E393">
+        <v>1864</v>
+      </c>
+      <c r="F393" t="s">
+        <v>49</v>
+      </c>
+      <c r="G393" t="s">
+        <v>38</v>
+      </c>
+      <c r="H393" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I393" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J393" s="2">
+        <v>0</v>
+      </c>
+      <c r="K393" s="1">
+        <v>46213.808333333334</v>
+      </c>
+      <c r="L393">
+        <v>0</v>
+      </c>
+      <c r="M393" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="394" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H394" s="2"/>
-      <c r="I394" s="1"/>
-      <c r="J394" s="2"/>
-      <c r="K394" s="1"/>
+      <c r="D394" t="s">
+        <v>36</v>
+      </c>
+      <c r="E394">
+        <v>1870</v>
+      </c>
+      <c r="F394" t="s">
+        <v>51</v>
+      </c>
+      <c r="G394" t="s">
+        <v>38</v>
+      </c>
+      <c r="H394" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I394" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J394" s="2">
+        <v>0</v>
+      </c>
+      <c r="K394" s="1">
+        <v>46213.809027777781</v>
+      </c>
+      <c r="L394">
+        <v>0</v>
+      </c>
+      <c r="M394" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="395" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H395" s="2"/>
-      <c r="I395" s="1"/>
-      <c r="J395" s="2"/>
-      <c r="K395" s="1"/>
+      <c r="D395" t="s">
+        <v>36</v>
+      </c>
+      <c r="E395">
+        <v>1867</v>
+      </c>
+      <c r="F395" t="s">
+        <v>52</v>
+      </c>
+      <c r="G395" t="s">
+        <v>38</v>
+      </c>
+      <c r="H395" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I395" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J395" s="2">
+        <v>0</v>
+      </c>
+      <c r="K395" s="1">
+        <v>46213.80972222222</v>
+      </c>
+      <c r="L395">
+        <v>0</v>
+      </c>
+      <c r="M395" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="396" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H396" s="2"/>
@@ -47447,7 +47678,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Atlantic-Foods\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49CCAAC8-96C3-4D9D-88E4-626C52B8DC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58507FF7-3754-4763-92EE-99BF67F78724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,10 +86,13 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
   </si>
   <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Backing Commercial Vehicles</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -101,40 +104,37 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Distracted Driving</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>Backing Commercial Vehicles</t>
-  </si>
-  <si>
-    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -692,7 +692,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
@@ -733,7 +733,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="1"/>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
@@ -774,7 +774,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
@@ -879,7 +879,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="1"/>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
@@ -920,7 +920,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
@@ -1057,7 +1057,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="1"/>
       <c r="M18" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
@@ -1130,7 +1130,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="1"/>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
@@ -1152,7 +1152,7 @@
       <c r="I22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="2">
         <v>0</v>
       </c>
       <c r="K22" s="1">
@@ -1171,7 +1171,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="1"/>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
@@ -1244,7 +1244,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1285,7 +1285,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="1"/>
       <c r="M28" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
@@ -1326,7 +1326,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="1"/>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
@@ -1431,7 +1431,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
       <c r="M34" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
@@ -1472,7 +1472,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="1"/>
       <c r="M36" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
@@ -1577,7 +1577,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
@@ -1650,7 +1650,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="1"/>
       <c r="M43" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
@@ -1691,7 +1691,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="1"/>
       <c r="M45" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
@@ -1796,7 +1796,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="1"/>
       <c r="M49" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
@@ -1933,7 +1933,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="1"/>
       <c r="M54" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
@@ -1974,7 +1974,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
       <c r="M56" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
@@ -2079,7 +2079,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="1"/>
       <c r="M60" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
@@ -2120,7 +2120,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="1"/>
       <c r="M62" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
@@ -2326,7 +2326,7 @@
         <v>38</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>13</v>
@@ -2358,7 +2358,7 @@
         <v>38</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2390,7 +2390,7 @@
         <v>38</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>12</v>
@@ -2414,7 +2414,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
@@ -2431,7 +2431,7 @@
         <v>38</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>13</v>
@@ -2463,7 +2463,7 @@
         <v>38</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>14</v>
@@ -2487,7 +2487,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="1"/>
       <c r="M75" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
@@ -2501,7 +2501,7 @@
         <v>56</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2533,7 +2533,7 @@
         <v>38</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>14</v>
@@ -2557,7 +2557,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="1"/>
       <c r="M78" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
@@ -2574,7 +2574,7 @@
         <v>38</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>14</v>
@@ -2598,7 +2598,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="1"/>
       <c r="M80" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
@@ -2615,7 +2615,7 @@
         <v>38</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>13</v>
@@ -2647,7 +2647,7 @@
         <v>38</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>13</v>
@@ -2679,7 +2679,7 @@
         <v>38</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>14</v>
@@ -2703,7 +2703,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="1"/>
       <c r="M84" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
@@ -2720,7 +2720,7 @@
         <v>38</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>14</v>
@@ -2744,7 +2744,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="1"/>
       <c r="M86" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
@@ -2761,7 +2761,7 @@
         <v>38</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>12</v>
@@ -2785,7 +2785,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
       <c r="M88" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
@@ -2802,7 +2802,7 @@
         <v>38</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -2834,7 +2834,7 @@
         <v>38</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -2866,7 +2866,7 @@
         <v>38</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>12</v>
@@ -2890,7 +2890,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="1"/>
       <c r="M92" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
@@ -2907,7 +2907,7 @@
         <v>38</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -2939,7 +2939,7 @@
         <v>38</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>12</v>
@@ -2963,7 +2963,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
       <c r="M95" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
@@ -2977,7 +2977,7 @@
         <v>56</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>13</v>
@@ -3009,7 +3009,7 @@
         <v>38</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3041,7 +3041,7 @@
         <v>38</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3073,7 +3073,7 @@
         <v>38</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3105,7 +3105,7 @@
         <v>38</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3137,7 +3137,7 @@
         <v>38</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3169,7 +3169,7 @@
         <v>38</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3201,7 +3201,7 @@
         <v>38</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       <c r="J109" s="2"/>
       <c r="K109" s="1"/>
       <c r="M109" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
@@ -3655,7 +3655,7 @@
         <v>38</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>13</v>
@@ -3687,7 +3687,7 @@
         <v>38</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>13</v>
@@ -3719,7 +3719,7 @@
         <v>38</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3751,7 +3751,7 @@
         <v>38</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3783,7 +3783,7 @@
         <v>38</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>12</v>
@@ -3807,7 +3807,7 @@
       <c r="J123" s="2"/>
       <c r="K123" s="1"/>
       <c r="M123" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
@@ -3821,7 +3821,7 @@
         <v>56</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -3853,7 +3853,7 @@
         <v>38</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -3885,7 +3885,7 @@
         <v>38</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -3917,7 +3917,7 @@
         <v>38</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -3949,7 +3949,7 @@
         <v>38</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -3981,7 +3981,7 @@
         <v>38</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4013,7 +4013,7 @@
         <v>38</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>12</v>
@@ -4037,7 +4037,7 @@
       <c r="J131" s="2"/>
       <c r="K131" s="1"/>
       <c r="M131" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
@@ -4054,7 +4054,7 @@
         <v>38</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4086,7 +4086,7 @@
         <v>38</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4118,7 +4118,7 @@
         <v>38</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>13</v>
@@ -4150,7 +4150,7 @@
         <v>38</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>13</v>
@@ -4182,7 +4182,7 @@
         <v>38</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4214,7 +4214,7 @@
         <v>38</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>14</v>
@@ -4238,7 +4238,7 @@
       <c r="J138" s="2"/>
       <c r="K138" s="1"/>
       <c r="M138" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
@@ -4252,7 +4252,7 @@
         <v>56</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4284,7 +4284,7 @@
         <v>38</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4316,7 +4316,7 @@
         <v>38</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4348,7 +4348,7 @@
         <v>38</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4380,7 +4380,7 @@
         <v>38</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4412,7 +4412,7 @@
         <v>38</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4444,7 +4444,7 @@
         <v>38</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>13</v>
@@ -4476,7 +4476,7 @@
         <v>38</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4921,7 +4921,7 @@
         <v>38</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -4953,7 +4953,7 @@
         <v>38</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -4985,7 +4985,7 @@
         <v>38</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>14</v>
@@ -5009,7 +5009,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -5026,7 +5026,7 @@
         <v>38</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -5058,7 +5058,7 @@
         <v>38</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5087,7 +5087,7 @@
         <v>56</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5119,7 +5119,7 @@
         <v>38</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>12</v>
@@ -5143,7 +5143,7 @@
       <c r="J168" s="2"/>
       <c r="K168" s="1"/>
       <c r="M168" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
@@ -5160,7 +5160,7 @@
         <v>38</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>13</v>
@@ -5192,7 +5192,7 @@
         <v>38</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>13</v>
@@ -5224,7 +5224,7 @@
         <v>38</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>13</v>
@@ -5256,7 +5256,7 @@
         <v>38</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>13</v>
@@ -5288,7 +5288,7 @@
         <v>38</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>12</v>
@@ -5312,7 +5312,7 @@
       <c r="J174" s="2"/>
       <c r="K174" s="1"/>
       <c r="M174" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
@@ -5329,7 +5329,7 @@
         <v>38</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5361,7 +5361,7 @@
         <v>38</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5393,7 +5393,7 @@
         <v>38</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>13</v>
@@ -5425,7 +5425,7 @@
         <v>38</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>13</v>
@@ -5457,7 +5457,7 @@
         <v>38</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>14</v>
@@ -5481,7 +5481,7 @@
       <c r="J180" s="2"/>
       <c r="K180" s="1"/>
       <c r="M180" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
@@ -5498,7 +5498,7 @@
         <v>38</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>12</v>
@@ -5522,7 +5522,7 @@
       <c r="J182" s="2"/>
       <c r="K182" s="1"/>
       <c r="M182" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
@@ -5536,7 +5536,7 @@
         <v>56</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>13</v>
@@ -5568,7 +5568,7 @@
         <v>38</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>10</v>
@@ -5600,7 +5600,7 @@
         <v>38</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -5632,7 +5632,7 @@
         <v>38</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>14</v>
@@ -5656,7 +5656,7 @@
       <c r="J187" s="2"/>
       <c r="K187" s="1"/>
       <c r="M187" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
@@ -5673,7 +5673,7 @@
         <v>38</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>12</v>
@@ -5697,7 +5697,7 @@
       <c r="J189" s="2"/>
       <c r="K189" s="1"/>
       <c r="M189" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
@@ -5714,7 +5714,7 @@
         <v>38</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5746,7 +5746,7 @@
         <v>38</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5778,7 +5778,7 @@
         <v>38</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5807,7 +5807,7 @@
         <v>58</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5839,7 +5839,7 @@
         <v>38</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>13</v>
@@ -5871,7 +5871,7 @@
         <v>38</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -5903,7 +5903,7 @@
         <v>38</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>13</v>
@@ -5935,7 +5935,7 @@
         <v>38</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -5967,7 +5967,7 @@
         <v>38</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>12</v>
@@ -5991,7 +5991,7 @@
       <c r="J199" s="2"/>
       <c r="K199" s="1"/>
       <c r="M199" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
@@ -6008,7 +6008,7 @@
         <v>38</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>12</v>
@@ -6032,7 +6032,7 @@
       <c r="J201" s="2"/>
       <c r="K201" s="1"/>
       <c r="M201" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
@@ -6049,7 +6049,7 @@
         <v>38</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>13</v>
@@ -6081,7 +6081,7 @@
         <v>38</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>13</v>
@@ -6113,7 +6113,7 @@
         <v>38</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>13</v>
@@ -6145,7 +6145,7 @@
         <v>38</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>13</v>
@@ -6177,7 +6177,7 @@
         <v>38</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>13</v>
@@ -6209,7 +6209,7 @@
         <v>38</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6238,7 +6238,7 @@
         <v>58</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>10</v>
@@ -6270,7 +6270,7 @@
         <v>38</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6302,7 +6302,7 @@
         <v>38</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>12</v>
@@ -6326,7 +6326,7 @@
       <c r="J211" s="2"/>
       <c r="K211" s="1"/>
       <c r="M211" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
@@ -6343,7 +6343,7 @@
         <v>38</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>12</v>
@@ -6367,7 +6367,7 @@
       <c r="J213" s="2"/>
       <c r="K213" s="1"/>
       <c r="M213" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
@@ -6384,7 +6384,7 @@
         <v>38</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6416,7 +6416,7 @@
         <v>38</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6448,7 +6448,7 @@
         <v>38</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>13</v>
@@ -6480,7 +6480,7 @@
         <v>38</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6512,7 +6512,7 @@
         <v>38</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6544,7 +6544,7 @@
         <v>38</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6576,7 +6576,7 @@
         <v>38</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>10</v>
@@ -6608,7 +6608,7 @@
         <v>38</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>13</v>
@@ -6640,7 +6640,7 @@
         <v>38</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6789,7 +6789,7 @@
       <c r="J227" s="2"/>
       <c r="K227" s="1"/>
       <c r="M227" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
@@ -6830,7 +6830,7 @@
       <c r="J229" s="2"/>
       <c r="K229" s="1"/>
       <c r="M229" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
@@ -7031,7 +7031,7 @@
       <c r="J236" s="2"/>
       <c r="K236" s="1"/>
       <c r="M236" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
@@ -7109,7 +7109,7 @@
         <v>58</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7141,7 +7141,7 @@
         <v>38</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7173,7 +7173,7 @@
         <v>38</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>13</v>
@@ -7205,7 +7205,7 @@
         <v>38</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>13</v>
@@ -7237,7 +7237,7 @@
         <v>38</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7269,7 +7269,7 @@
         <v>38</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7301,7 +7301,7 @@
         <v>38</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>13</v>
@@ -7333,7 +7333,7 @@
         <v>38</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7365,7 +7365,7 @@
         <v>38</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>13</v>
@@ -7397,7 +7397,7 @@
         <v>38</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>13</v>
@@ -7429,7 +7429,7 @@
         <v>38</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7461,7 +7461,7 @@
         <v>38</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7493,7 +7493,7 @@
         <v>38</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7642,7 +7642,7 @@
       <c r="J256" s="2"/>
       <c r="K256" s="1"/>
       <c r="M256" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
@@ -7683,7 +7683,7 @@
       <c r="J258" s="2"/>
       <c r="K258" s="1"/>
       <c r="M258" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
@@ -7884,7 +7884,7 @@
       <c r="J265" s="2"/>
       <c r="K265" s="1"/>
       <c r="M265" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
@@ -7962,7 +7962,7 @@
         <v>58</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -7994,7 +7994,7 @@
         <v>38</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>12</v>
@@ -8018,7 +8018,7 @@
       <c r="J270" s="2"/>
       <c r="K270" s="1"/>
       <c r="M270" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
@@ -8035,7 +8035,7 @@
         <v>38</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>10</v>
@@ -8067,7 +8067,7 @@
         <v>38</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>12</v>
@@ -8091,7 +8091,7 @@
       <c r="J273" s="2"/>
       <c r="K273" s="1"/>
       <c r="M273" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
@@ -8108,7 +8108,7 @@
         <v>38</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -8140,7 +8140,7 @@
         <v>38</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -8172,7 +8172,7 @@
         <v>38</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>13</v>
@@ -8204,7 +8204,7 @@
         <v>38</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>12</v>
@@ -8228,7 +8228,7 @@
       <c r="J278" s="2"/>
       <c r="K278" s="1"/>
       <c r="M278" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="279" spans="4:13" x14ac:dyDescent="0.3">
@@ -8245,7 +8245,7 @@
         <v>38</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8277,7 +8277,7 @@
         <v>38</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>10</v>
@@ -8426,7 +8426,7 @@
       <c r="J285" s="2"/>
       <c r="K285" s="1"/>
       <c r="M285" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
@@ -8632,7 +8632,7 @@
         <v>58</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8664,7 +8664,7 @@
         <v>38</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>13</v>
@@ -8696,7 +8696,7 @@
         <v>38</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>10</v>
@@ -8728,7 +8728,7 @@
         <v>38</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>13</v>
@@ -8760,7 +8760,7 @@
         <v>38</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8792,7 +8792,7 @@
         <v>38</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>10</v>
@@ -8824,7 +8824,7 @@
         <v>38</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>13</v>
@@ -8856,7 +8856,7 @@
         <v>38</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -8888,7 +8888,7 @@
         <v>38</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -8920,7 +8920,7 @@
         <v>38</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>10</v>
@@ -8952,7 +8952,7 @@
         <v>38</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>13</v>
@@ -8984,7 +8984,7 @@
         <v>38</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -9016,7 +9016,7 @@
         <v>38</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -9048,7 +9048,7 @@
         <v>38</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>13</v>
@@ -9080,7 +9080,7 @@
         <v>38</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>13</v>
@@ -9112,7 +9112,7 @@
         <v>38</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>13</v>
@@ -9144,7 +9144,7 @@
         <v>38</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>13</v>
@@ -9176,7 +9176,7 @@
         <v>38</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>13</v>
@@ -9205,7 +9205,7 @@
         <v>61</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -9234,7 +9234,7 @@
         <v>62</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>13</v>
@@ -9263,7 +9263,7 @@
         <v>63</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>13</v>
@@ -9635,7 +9635,7 @@
         <v>61</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>12</v>
@@ -9659,7 +9659,7 @@
       <c r="J325" s="2"/>
       <c r="K325" s="1"/>
       <c r="M325" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="326" spans="4:13" x14ac:dyDescent="0.3">
@@ -9673,7 +9673,7 @@
         <v>61</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>10</v>
@@ -9705,7 +9705,7 @@
         <v>38</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>10</v>
@@ -9737,7 +9737,7 @@
         <v>38</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>12</v>
@@ -9761,7 +9761,7 @@
       <c r="J329" s="2"/>
       <c r="K329" s="1"/>
       <c r="M329" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="330" spans="4:13" x14ac:dyDescent="0.3">
@@ -9778,7 +9778,7 @@
         <v>38</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9810,7 +9810,7 @@
         <v>38</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9842,7 +9842,7 @@
         <v>38</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -9871,7 +9871,7 @@
         <v>62</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>10</v>
@@ -9900,7 +9900,7 @@
         <v>63</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>38</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>10</v>
@@ -9964,7 +9964,7 @@
         <v>38</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -9996,7 +9996,7 @@
         <v>38</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>10</v>
@@ -10025,7 +10025,7 @@
         <v>61</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>14</v>
@@ -10049,7 +10049,7 @@
       <c r="J339" s="2"/>
       <c r="K339" s="1"/>
       <c r="M339" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="340" spans="4:13" x14ac:dyDescent="0.3">
@@ -10066,7 +10066,7 @@
         <v>38</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -10098,7 +10098,7 @@
         <v>38</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>12</v>
@@ -10122,7 +10122,7 @@
       <c r="J342" s="2"/>
       <c r="K342" s="1"/>
       <c r="M342" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="343" spans="4:13" x14ac:dyDescent="0.3">
@@ -10139,7 +10139,7 @@
         <v>38</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -10171,7 +10171,7 @@
         <v>38</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>10</v>
@@ -10203,7 +10203,7 @@
         <v>38</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -10232,7 +10232,7 @@
         <v>63</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10264,7 +10264,7 @@
         <v>38</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -10296,7 +10296,7 @@
         <v>38</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10328,7 +10328,7 @@
         <v>38</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10357,7 +10357,7 @@
         <v>64</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>10</v>
@@ -10386,7 +10386,7 @@
         <v>61</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>10</v>
@@ -10418,7 +10418,7 @@
         <v>38</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>10</v>
@@ -10450,7 +10450,7 @@
         <v>38</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>12</v>
@@ -10474,7 +10474,7 @@
       <c r="J354" s="2"/>
       <c r="K354" s="1"/>
       <c r="M354" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="355" spans="4:13" x14ac:dyDescent="0.3">
@@ -10491,7 +10491,7 @@
         <v>38</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10520,7 +10520,7 @@
         <v>64</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10552,7 +10552,7 @@
         <v>38</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>10</v>
@@ -10584,7 +10584,7 @@
         <v>38</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>13</v>
@@ -10613,7 +10613,7 @@
         <v>63</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>10</v>
@@ -10645,7 +10645,7 @@
         <v>38</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>10</v>
@@ -10677,7 +10677,7 @@
         <v>38</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>10</v>
@@ -10709,7 +10709,7 @@
         <v>38</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>10</v>
@@ -10738,7 +10738,7 @@
         <v>61</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>10</v>
@@ -10770,7 +10770,7 @@
         <v>38</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>10</v>
@@ -10802,7 +10802,7 @@
         <v>38</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>12</v>
@@ -10826,7 +10826,7 @@
       <c r="J366" s="2"/>
       <c r="K366" s="1"/>
       <c r="M366" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="367" spans="4:13" x14ac:dyDescent="0.3">
@@ -10843,7 +10843,7 @@
         <v>38</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>10</v>
@@ -10872,7 +10872,7 @@
         <v>64</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>13</v>
@@ -10904,7 +10904,7 @@
         <v>38</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>10</v>
@@ -10936,7 +10936,7 @@
         <v>38</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>13</v>
@@ -10965,7 +10965,7 @@
         <v>63</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>13</v>
@@ -10997,7 +10997,7 @@
         <v>38</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>10</v>
@@ -11029,7 +11029,7 @@
         <v>38</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>13</v>
@@ -11061,7 +11061,7 @@
         <v>38</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>10</v>
@@ -11093,7 +11093,7 @@
         <v>38</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -11125,7 +11125,7 @@
         <v>38</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -11154,7 +11154,7 @@
         <v>61</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>10</v>
@@ -11186,7 +11186,7 @@
         <v>38</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -11218,7 +11218,7 @@
         <v>38</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>13</v>
@@ -11247,7 +11247,7 @@
         <v>64</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>13</v>
@@ -11279,7 +11279,7 @@
         <v>38</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>12</v>
@@ -11303,7 +11303,7 @@
       <c r="J382" s="2"/>
       <c r="K382" s="1"/>
       <c r="M382" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="383" spans="4:13" x14ac:dyDescent="0.3">
@@ -11320,7 +11320,7 @@
         <v>38</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>13</v>
@@ -11349,7 +11349,7 @@
         <v>63</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>13</v>
@@ -11381,7 +11381,7 @@
         <v>38</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>10</v>
@@ -11413,7 +11413,7 @@
         <v>38</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>10</v>
@@ -11442,13 +11442,13 @@
         <v>61</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J387" s="2">
-        <v>0</v>
+        <v>1.125E-2</v>
       </c>
       <c r="K387" s="1">
         <v>46213.805555555555</v>
@@ -11474,7 +11474,7 @@
         <v>38</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>13</v>
@@ -11506,7 +11506,7 @@
         <v>38</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>13</v>
@@ -11538,13 +11538,13 @@
         <v>38</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I390" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J390" s="2">
-        <v>0</v>
+        <v>7.1064814814814819E-3</v>
       </c>
       <c r="K390" s="1">
         <v>46213.806944444441</v>
@@ -11570,13 +11570,13 @@
         <v>38</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I391" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J391" s="2">
-        <v>0</v>
+        <v>7.4189814814814813E-3</v>
       </c>
       <c r="K391" s="1">
         <v>46213.807638888888</v>
@@ -11602,7 +11602,7 @@
         <v>38</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>13</v>
@@ -11634,13 +11634,13 @@
         <v>38</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I393" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J393" s="2">
-        <v>0</v>
+        <v>6.030092592592593E-3</v>
       </c>
       <c r="K393" s="1">
         <v>46213.808333333334</v>
@@ -11666,7 +11666,7 @@
         <v>38</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>13</v>
@@ -11698,13 +11698,13 @@
         <v>38</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I395" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J395" s="2">
-        <v>0</v>
+        <v>6.7129629629629631E-3</v>
       </c>
       <c r="K395" s="1">
         <v>46213.80972222222</v>
@@ -12175,6 +12175,7 @@
     <row r="472" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H472" s="2"/>
       <c r="I472" s="1"/>
+      <c r="J472" s="2"/>
       <c r="K472" s="1"/>
     </row>
     <row r="473" spans="8:11" x14ac:dyDescent="0.3">
@@ -13523,6 +13524,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -13832,6 +13834,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -13921,6 +13924,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -14027,6 +14031,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -14044,6 +14049,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -14055,6 +14061,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -14096,6 +14103,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -14119,6 +14127,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -14142,6 +14151,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -14159,6 +14169,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -14170,11 +14181,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -14294,6 +14307,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -14377,6 +14391,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -14400,6 +14415,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -14411,6 +14427,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -14422,6 +14439,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -14469,6 +14487,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -14522,6 +14541,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -14694,6 +14714,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -14705,6 +14726,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -14782,6 +14804,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -14799,6 +14822,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -14846,6 +14870,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -14958,6 +14983,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -15017,6 +15043,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -15028,6 +15055,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -15099,6 +15127,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -15151,6 +15180,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -15227,11 +15257,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -15291,6 +15323,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -15302,6 +15335,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -15313,11 +15347,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -15371,6 +15407,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -15387,6 +15424,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -15410,6 +15448,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -15427,6 +15466,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -15473,11 +15513,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -15519,11 +15561,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -15541,6 +15585,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -15552,6 +15597,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -15563,6 +15609,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -15580,6 +15627,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -15657,6 +15705,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -15686,6 +15735,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -15697,16 +15747,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -15718,16 +15771,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -15739,11 +15795,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -15767,6 +15825,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -15808,6 +15867,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -15837,21 +15897,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -15863,6 +15927,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -15880,6 +15945,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -15919,11 +15985,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -15971,6 +16039,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -16000,6 +16069,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -16076,6 +16146,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -16122,6 +16193,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -16157,11 +16229,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -16178,6 +16252,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -16188,6 +16263,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -16223,6 +16299,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -16234,6 +16311,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -16245,6 +16323,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -16256,6 +16335,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -16267,6 +16347,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -16308,6 +16389,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -16325,6 +16407,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -16342,6 +16425,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -16383,6 +16467,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -16406,6 +16491,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -16452,6 +16538,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -16487,6 +16574,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -16510,6 +16598,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -16550,6 +16639,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -16567,11 +16657,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -16630,6 +16722,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -16646,6 +16739,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -16657,6 +16751,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -16668,11 +16763,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -16708,6 +16805,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -16760,6 +16858,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -16770,6 +16869,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -16785,6 +16885,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -16808,16 +16909,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -16888,6 +16992,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -16899,6 +17004,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -16999,6 +17105,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -17055,6 +17163,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -17078,6 +17187,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -17202,6 +17312,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -17360,6 +17471,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -17377,6 +17489,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -17417,6 +17530,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -17749,6 +17863,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -17837,6 +17952,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -17930,6 +18046,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -17989,11 +18106,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -18045,6 +18164,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -18086,6 +18206,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -18130,6 +18251,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -18176,11 +18298,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -18378,6 +18502,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -18407,6 +18532,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -18422,6 +18549,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -18481,6 +18609,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -18552,6 +18681,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -18593,6 +18723,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -18711,6 +18842,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -18775,6 +18907,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -18899,6 +19032,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -19125,6 +19259,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -19242,6 +19377,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -19325,6 +19461,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -19384,6 +19521,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -19407,6 +19545,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -19454,6 +19593,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -19513,6 +19653,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -19536,6 +19677,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -19553,6 +19695,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -19636,6 +19779,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -19827,6 +19971,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -47683,6 +47828,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -47690,6 +47836,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -47697,6 +47844,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -47712,6 +47860,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -47721,6 +47870,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -47728,9 +47878,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -47738,12 +47894,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -47751,12 +47910,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -47768,9 +47930,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -47785,6 +47949,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -47811,6 +47976,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -47821,7 +47987,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -47829,6 +48000,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -47840,6 +48012,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -47847,6 +48020,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -47861,13 +48035,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -47878,15 +48058,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -47902,6 +48085,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -47920,6 +48104,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -47931,6 +48116,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -47948,18 +48134,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -47988,6 +48179,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -47995,9 +48187,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -48020,12 +48214,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -48040,9 +48237,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -48058,12 +48257,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -48084,6 +48285,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -48095,9 +48297,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -48109,6 +48313,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -48148,9 +48353,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -48158,9 +48365,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -48171,6 +48380,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -48178,18 +48388,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -48197,6 +48415,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -48207,6 +48426,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -48233,15 +48453,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -48263,6 +48487,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -48270,9 +48495,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -48280,6 +48507,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -48291,6 +48519,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -48305,6 +48534,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -48314,6 +48547,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -48325,6 +48559,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -48335,10 +48570,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -48346,6 +48586,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -48360,6 +48601,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -48382,6 +48624,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -48401,25 +48644,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -48427,6 +48682,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -48434,15 +48690,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -48456,6 +48719,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -48474,9 +48738,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -48484,9 +48750,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -48494,6 +48762,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -48510,10 +48779,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
